--- a/data/city_corr_with_coords.xlsx
+++ b/data/city_corr_with_coords.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -493,521 +493,521 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>Казань</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5331.32890201871</v>
+        <v>6859.175644028103</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9528808721088646</v>
+        <v>0.9812637809248471</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9485505488371949</v>
+        <v>0.9769473318612447</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9442042958948598</v>
+        <v>0.9704218412258898</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9546165920078864</v>
+        <v>0.9839360077388425</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9720457717101963</v>
+        <v>0.9912852287461863</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.04766524214672133</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02047436805558642</v>
+        <v>0.05385624944710464</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04331792293259478</v>
+        <v>0.03517398410670085</v>
       </c>
       <c r="K2" t="n">
-        <v>55.75205144422111</v>
+        <v>55.79445056017505</v>
       </c>
       <c r="L2" t="n">
-        <v>37.60109972035175</v>
+        <v>49.13246562800875</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Чебоксары</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6860.212121212121</v>
+        <v>4117.823529411765</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9812637809248471</v>
+        <v>0.9760374506321022</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9769473318612447</v>
+        <v>0.9705206535742379</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9704218412258898</v>
+        <v>0.9859520008625056</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9839360077388425</v>
+        <v>0.9765168349055965</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9912852287461863</v>
+        <v>0.9924721580400689</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07028981624098166</v>
+        <v>0.05324893548963439</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0537962844438596</v>
+        <v>0.14481076245816</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04989532092284753</v>
+        <v>0.03703476340845585</v>
       </c>
       <c r="K3" t="n">
-        <v>55.79445056017505</v>
+        <v>56.12782812037037</v>
       </c>
       <c r="L3" t="n">
-        <v>49.13246562800875</v>
+        <v>47.24983348148148</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Сургут</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3795.71186440678</v>
+        <v>5332.632047477745</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9633280907223243</v>
+        <v>0.9528808721088646</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9373660358243351</v>
+        <v>0.9485505488371949</v>
       </c>
       <c r="E4" t="n">
-        <v>0.986318840081251</v>
+        <v>0.9442042958948598</v>
       </c>
       <c r="F4" t="n">
-        <v>0.951735781043868</v>
+        <v>0.9546165920078864</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9875449668652794</v>
+        <v>0.9720457717101963</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07696368461309805</v>
+        <v>0.02303929858205748</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1229852236533005</v>
+        <v>0.02053313928613889</v>
       </c>
       <c r="J4" t="n">
-        <v>0.06557072658184385</v>
+        <v>0.05115128445049433</v>
       </c>
       <c r="K4" t="n">
-        <v>61.26106533532935</v>
+        <v>55.75205144422111</v>
       </c>
       <c r="L4" t="n">
-        <v>73.40036158682635</v>
+        <v>37.60109972035175</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Екатеринбург</t>
+          <t>Сургут</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4653.449814126394</v>
+        <v>3795.71186440678</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9726753442044936</v>
+        <v>0.9633280907223243</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9375686739536877</v>
+        <v>0.9373660358243351</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9371283888437367</v>
+        <v>0.986318840081251</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9844033868722522</v>
+        <v>0.951735781043868</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9791437023627492</v>
+        <v>0.9875449668652794</v>
       </c>
       <c r="H5" t="n">
-        <v>0.08010460038764587</v>
+        <v>0.07232892694757313</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04336685705515497</v>
+        <v>0.1229852236533005</v>
       </c>
       <c r="J5" t="n">
-        <v>0.06965512502271137</v>
+        <v>0.05629854051425557</v>
       </c>
       <c r="K5" t="n">
-        <v>56.83069912717537</v>
+        <v>61.26106533532935</v>
       </c>
       <c r="L5" t="n">
-        <v>60.604742854083</v>
+        <v>73.40036158682635</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Нижневартовск</t>
+          <t>Архангельск</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4119.904761904761</v>
+        <v>4198.764705882353</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9781592427629623</v>
+        <v>0.9708395068175809</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9566952971248306</v>
+        <v>0.9671780444997763</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9702542433729709</v>
+        <v>0.9857465473964742</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9623570643387477</v>
+        <v>0.9762171179859211</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9888573406449988</v>
+        <v>0.99422552461875</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1190466495248848</v>
+        <v>0.1141302784079595</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1327096768149853</v>
+        <v>0.1368266306599069</v>
       </c>
       <c r="J6" t="n">
-        <v>0.07925236538033084</v>
+        <v>0.05975724071547263</v>
       </c>
       <c r="K6" t="n">
-        <v>60.93856452173912</v>
+        <v>64.53560009195402</v>
       </c>
       <c r="L6" t="n">
-        <v>76.57221518840579</v>
+        <v>40.55799275862068</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Уфа</t>
+          <t>Саранск</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4591.90625</v>
+        <v>5943.375</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9751552486435551</v>
+        <v>0.9619139009133288</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9489444430003235</v>
+        <v>0.9416590962952297</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9896032054264972</v>
+        <v>0.8514733393719389</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9841795694522694</v>
+        <v>0.9682209769809312</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9834134068907898</v>
+        <v>0.9882742012667537</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1403304109303485</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04347393311479548</v>
+        <v>0.2091508153003799</v>
       </c>
       <c r="J7" t="n">
-        <v>0.08099851460108269</v>
+        <v>0.06185113717072678</v>
       </c>
       <c r="K7" t="n">
-        <v>54.73839056774193</v>
+        <v>54.19180517948718</v>
       </c>
       <c r="L7" t="n">
-        <v>55.9902713516129</v>
+        <v>45.17717769230769</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Чебоксары</t>
+          <t>Екатеринбург</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4117.823529411765</v>
+        <v>4669.74716981132</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9760374506321022</v>
+        <v>0.9726753442044936</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9705206535742379</v>
+        <v>0.9375686739536877</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9859520008625056</v>
+        <v>0.9371283888437367</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9765168349055965</v>
+        <v>0.9844033868722522</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9924721580400689</v>
+        <v>0.9791437023627492</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1448232186603507</v>
+        <v>0.084133578844631</v>
       </c>
       <c r="I8" t="n">
-        <v>0.14481076245816</v>
+        <v>0.04390061779305431</v>
       </c>
       <c r="J8" t="n">
-        <v>0.08265234155253445</v>
+        <v>0.06301451765932173</v>
       </c>
       <c r="K8" t="n">
-        <v>56.12782812037037</v>
+        <v>56.83069912717537</v>
       </c>
       <c r="L8" t="n">
-        <v>47.24983348148148</v>
+        <v>60.604742854083</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Самара</t>
+          <t>Калуга</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4222.941176470588</v>
+        <v>3680.464285714286</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9731195808453854</v>
+        <v>0.969909662287307</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9607594179384025</v>
+        <v>0.9549586530150018</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9831224658594395</v>
+        <v>0.9915638019290982</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9746740954586972</v>
+        <v>0.9318764393501597</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9877431348633141</v>
+        <v>0.9969145181678642</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1394371349536524</v>
+        <v>0.1011196452336617</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0501228107916176</v>
+        <v>0.1356768349944766</v>
       </c>
       <c r="J9" t="n">
-        <v>0.08339435427065069</v>
+        <v>0.06492683620851764</v>
       </c>
       <c r="K9" t="n">
-        <v>53.22946951639344</v>
+        <v>54.52259947572816</v>
       </c>
       <c r="L9" t="n">
-        <v>50.16079603073771</v>
+        <v>36.24974281553398</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ханты-Мансийск</t>
+          <t>Уфа</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4657.708333333333</v>
+        <v>4591.90625</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9897511250255331</v>
+        <v>0.9751552486435551</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9862198564671493</v>
+        <v>0.9489444430003235</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9364907039145117</v>
+        <v>0.9896032054264972</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9874799005590261</v>
+        <v>0.9841795694522694</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9940368584613205</v>
+        <v>0.9834134068907898</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1449303641921292</v>
+        <v>0.1352497460128791</v>
       </c>
       <c r="I10" t="n">
-        <v>0.167775556426339</v>
+        <v>0.04347393311479548</v>
       </c>
       <c r="J10" t="n">
-        <v>0.08690169611505093</v>
+        <v>0.06523804743610824</v>
       </c>
       <c r="K10" t="n">
-        <v>61.00434712280702</v>
+        <v>54.73839056774193</v>
       </c>
       <c r="L10" t="n">
-        <v>69.04070875438597</v>
+        <v>55.9902713516129</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Санкт-Петербург</t>
+          <t>Самара</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5278.383928571428</v>
+        <v>4222.941176470588</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9800540913978991</v>
+        <v>0.9731195808453854</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9785201224280055</v>
+        <v>0.9607594179384025</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8311032772097571</v>
+        <v>0.9831224658594395</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9807603244302355</v>
+        <v>0.9746740954586972</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9839309024627281</v>
+        <v>0.9877431348633141</v>
       </c>
       <c r="H11" t="n">
-        <v>0.08181894613073445</v>
+        <v>0.1277520237177687</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02225244257084506</v>
+        <v>0.0501228107916176</v>
       </c>
       <c r="J11" t="n">
-        <v>0.09062674766798304</v>
+        <v>0.06547770295508501</v>
       </c>
       <c r="K11" t="n">
-        <v>59.93266165205871</v>
+        <v>53.22946951639344</v>
       </c>
       <c r="L11" t="n">
-        <v>30.32795220383204</v>
+        <v>50.16079603073771</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Саранск</t>
+          <t>Санкт-Петербург</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5943.375</v>
+        <v>5276.452644526446</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9619139009133288</v>
+        <v>0.9800540913978991</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9416590962952297</v>
+        <v>0.9785201224280055</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8514733393719389</v>
+        <v>0.8311032772097571</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9682209769809312</v>
+        <v>0.9807603244302355</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9882742012667537</v>
+        <v>0.9839309024627281</v>
       </c>
       <c r="H12" t="n">
-        <v>0.08295786186293029</v>
+        <v>0.05879910637423909</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2091508153003799</v>
+        <v>0.02226958423108965</v>
       </c>
       <c r="J12" t="n">
-        <v>0.09835259639041612</v>
+        <v>0.07461810753770116</v>
       </c>
       <c r="K12" t="n">
-        <v>54.19180517948718</v>
+        <v>59.93266165205871</v>
       </c>
       <c r="L12" t="n">
-        <v>45.17717769230769</v>
+        <v>30.32795220383204</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Барнаул</t>
+          <t>Ульяновск</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3584.714285714286</v>
+        <v>4179.733333333334</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9618119225953397</v>
+        <v>0.9589602473925397</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9348466257203721</v>
+        <v>0.94965887529639</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9747139263148146</v>
+        <v>0.968952231398585</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9736890167958998</v>
+        <v>0.9611504412361787</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9920429950365743</v>
+        <v>0.9897110296820364</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1637310273882111</v>
+        <v>0.1245269334421972</v>
       </c>
       <c r="I13" t="n">
-        <v>0.06102483312118659</v>
+        <v>0.1007026277810645</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1027814243058771</v>
+        <v>0.07620197008169996</v>
       </c>
       <c r="K13" t="n">
-        <v>53.34145224705883</v>
+        <v>54.32241853012048</v>
       </c>
       <c r="L13" t="n">
-        <v>83.74447705294118</v>
+        <v>48.41170151807229</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Архангельск</t>
+          <t>Ханты-Мансийск</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4198.764705882353</v>
+        <v>4657.708333333333</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9708395068175809</v>
+        <v>0.9897511250255331</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9671780444997763</v>
+        <v>0.9862198564671493</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9857465473964742</v>
+        <v>0.9364907039145117</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9762171179859211</v>
+        <v>0.9874799005590261</v>
       </c>
       <c r="G14" t="n">
-        <v>0.99422552461875</v>
+        <v>0.9940368584613205</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1918343086007437</v>
+        <v>0.1576906645437193</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1368266306599069</v>
+        <v>0.167775556426339</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1053600418410936</v>
+        <v>0.07674716181537865</v>
       </c>
       <c r="K14" t="n">
-        <v>64.53560009195402</v>
+        <v>61.00434712280702</v>
       </c>
       <c r="L14" t="n">
-        <v>40.55799275862068</v>
+        <v>69.04070875438597</v>
       </c>
     </row>
     <row r="15">
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6527.450819672131</v>
+        <v>6528.078189300411</v>
       </c>
       <c r="C15" t="n">
         <v>0.9610019443235096</v>
@@ -1035,13 +1035,13 @@
         <v>0.9763356110373562</v>
       </c>
       <c r="H15" t="n">
-        <v>0.16992297408847</v>
+        <v>0.1351760892879805</v>
       </c>
       <c r="I15" t="n">
-        <v>0.05352338705917035</v>
+        <v>0.05370710647085594</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1064901908903009</v>
+        <v>0.07768395264928744</v>
       </c>
       <c r="K15" t="n">
         <v>56.30815029885057</v>
@@ -1053,881 +1053,881 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Кемерово</t>
+          <t>Тюмень</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3869.174603174603</v>
+        <v>4236.789808917198</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9828278534900422</v>
+        <v>0.9478374145504151</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9783234103052159</v>
+        <v>0.9047011732874324</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9918862030378047</v>
+        <v>0.973529805144457</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9828236725842834</v>
+        <v>0.9793758564764465</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9957532606877977</v>
+        <v>0.9966224046594959</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2143013134024265</v>
+        <v>0.1328150592331583</v>
       </c>
       <c r="I16" t="n">
-        <v>0.07870376265451108</v>
+        <v>0.05816036192441012</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1075091691461788</v>
+        <v>0.08266874797899354</v>
       </c>
       <c r="K16" t="n">
-        <v>55.34899745895522</v>
+        <v>57.14379044747899</v>
       </c>
       <c r="L16" t="n">
-        <v>86.11081777985073</v>
+        <v>65.55519158403362</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Калуга</t>
+          <t>Волгоград</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3680.464285714286</v>
+        <v>4345.178571428572</v>
       </c>
       <c r="C17" t="n">
-        <v>0.969909662287307</v>
+        <v>0.9602611468223854</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9549586530150018</v>
+        <v>0.9415701470623393</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9915638019290982</v>
+        <v>0.9775861800685594</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9318764393501597</v>
+        <v>0.9647861506793204</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9969145181678642</v>
+        <v>0.9856298234297227</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1758544384360838</v>
+        <v>0.1823984044617917</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1356768349944766</v>
+        <v>0.06309040867101477</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1079221097409495</v>
+        <v>0.09354967063123958</v>
       </c>
       <c r="K17" t="n">
-        <v>54.52259947572816</v>
+        <v>48.72100432075472</v>
       </c>
       <c r="L17" t="n">
-        <v>36.24974281553398</v>
+        <v>44.53555019245283</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Тобольск</t>
+          <t>Ярославль</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5058.863636363636</v>
+        <v>4896.162790697675</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9652986317769199</v>
+        <v>0.9757479291352548</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9619177682595972</v>
+        <v>0.9795981088894178</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9819995373056618</v>
+        <v>0.9904198546160858</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9831901002829951</v>
+        <v>0.9785033579180813</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9928387946386269</v>
+        <v>0.9961432762058868</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1973262863647113</v>
+        <v>0.2395678291132304</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1875958709052983</v>
+        <v>0.06697966049920988</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1094870252081701</v>
+        <v>0.09784372056572579</v>
       </c>
       <c r="K18" t="n">
-        <v>58.22035889795919</v>
+        <v>57.64236805555556</v>
       </c>
       <c r="L18" t="n">
-        <v>68.27821857142857</v>
+        <v>39.89045934188034</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ярославль</t>
+          <t>Астрахань</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4896.162790697675</v>
+        <v>3440.238805970149</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9757479291352548</v>
+        <v>0.9784383109912644</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9795981088894178</v>
+        <v>0.9315906499349267</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9904198546160858</v>
+        <v>0.9836314194782991</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9785033579180813</v>
+        <v>0.9579361924183152</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9961432762058868</v>
+        <v>0.994871644320056</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2165742130156177</v>
+        <v>0.2224311112546758</v>
       </c>
       <c r="I19" t="n">
-        <v>0.06697966049920988</v>
+        <v>0.07471430287303056</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1116833123940992</v>
+        <v>0.1030141343695109</v>
       </c>
       <c r="K19" t="n">
-        <v>57.64236805555556</v>
+        <v>46.35151272058823</v>
       </c>
       <c r="L19" t="n">
-        <v>39.89045934188034</v>
+        <v>48.0335039632353</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Томск</t>
+          <t>Саратов</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3757.434210526316</v>
+        <v>4217.022727272727</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9814168464835591</v>
+        <v>0.9740909092296519</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9474433314549505</v>
+        <v>0.9703381507659136</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9711280338166176</v>
+        <v>0.9746769514757834</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9847234133311041</v>
+        <v>0.9735788414714274</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9908600486584006</v>
+        <v>0.9906619954981383</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2060595738517248</v>
+        <v>0.2429141716246663</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1502091368758373</v>
+        <v>0.1123932398659774</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1127882019862464</v>
+        <v>0.1055430820059323</v>
       </c>
       <c r="K20" t="n">
-        <v>56.47955309271524</v>
+        <v>51.54124806976744</v>
       </c>
       <c r="L20" t="n">
-        <v>84.97116295364239</v>
+        <v>46.02896238372093</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Тюмень</t>
+          <t>Череповец</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4236.789808917198</v>
+        <v>4359.309523809524</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9478374145504151</v>
+        <v>0.9091858036120699</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9047011732874324</v>
+        <v>0.8654170197827892</v>
       </c>
       <c r="E21" t="n">
-        <v>0.973529805144457</v>
+        <v>0.9051915237541124</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9793758564764465</v>
+        <v>0.9335288191526564</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9966224046594959</v>
+        <v>0.9746623469301416</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1726150599402221</v>
+        <v>0.07784559403695587</v>
       </c>
       <c r="I21" t="n">
-        <v>0.05816036192441012</v>
+        <v>0.2263761534780582</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1134622542134174</v>
+        <v>0.1066146435905441</v>
       </c>
       <c r="K21" t="n">
-        <v>57.14379044747899</v>
+        <v>59.12204149999999</v>
       </c>
       <c r="L21" t="n">
-        <v>65.55519158403362</v>
+        <v>37.92426309722222</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Новокузнецк</t>
+          <t>Нижневартовск</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3965.836734693878</v>
+        <v>4119.904761904761</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9573833520516564</v>
+        <v>0.9781592427629623</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9426529956416373</v>
+        <v>0.9566952971248306</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9694972521263953</v>
+        <v>0.9702542433729709</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9531913880432364</v>
+        <v>0.9623570643387477</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9942867432620857</v>
+        <v>0.9888573406449988</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1773809373107214</v>
+        <v>0.2384805089562974</v>
       </c>
       <c r="I22" t="n">
-        <v>0.09132681733571003</v>
+        <v>0.1327096768149853</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1147435763240621</v>
+        <v>0.1079552126345227</v>
       </c>
       <c r="K22" t="n">
-        <v>53.76131239516129</v>
+        <v>60.93856452173912</v>
       </c>
       <c r="L22" t="n">
-        <v>87.14451374193548</v>
+        <v>76.57221518840579</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Новосибирск</t>
+          <t>Петрозаводск</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3969.708633093525</v>
+        <v>4123.292307692308</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9576789994465081</v>
+        <v>0.9440424732873276</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9201096265072215</v>
+        <v>0.9780737741625696</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9054029090854322</v>
+        <v>0.9882811373079512</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9696466828184448</v>
+        <v>0.987512242401591</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9868370838528687</v>
+        <v>0.9970319814628792</v>
       </c>
       <c r="H23" t="n">
-        <v>0.163038995879962</v>
+        <v>0.2496657870454436</v>
       </c>
       <c r="I23" t="n">
-        <v>0.02111490510345441</v>
+        <v>0.1075102883521822</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1236205625035979</v>
+        <v>0.1092973422112956</v>
       </c>
       <c r="K23" t="n">
-        <v>55.01271715303031</v>
+        <v>61.78167547580645</v>
       </c>
       <c r="L23" t="n">
-        <v>82.93194300606061</v>
+        <v>34.35349441129032</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Омск</t>
+          <t>Челябинск</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3393.263736263736</v>
+        <v>4141.106382978724</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9629392806787805</v>
+        <v>0.9552545051947455</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8152466907680476</v>
+        <v>0.8992518399398306</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9726954641339219</v>
+        <v>0.9637343474312238</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9814661157225163</v>
+        <v>0.9756389264163315</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9673126761059034</v>
+        <v>0.9883971471727957</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1828799920177547</v>
+        <v>0.2061918687627609</v>
       </c>
       <c r="I24" t="n">
-        <v>0.09979340677435521</v>
+        <v>0.08764507950318171</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1241034518635911</v>
+        <v>0.1093534466748473</v>
       </c>
       <c r="K24" t="n">
-        <v>54.98482156603773</v>
+        <v>55.16710053090909</v>
       </c>
       <c r="L24" t="n">
-        <v>73.35854933490566</v>
+        <v>61.37717588727273</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Волгоград</t>
+          <t>Ижевск</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4345.178571428572</v>
+        <v>5213.757575757576</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9602611468223854</v>
+        <v>0.9320572755513026</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9415701470623393</v>
+        <v>0.9258981928780242</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9775861800685594</v>
+        <v>0.9900469331197215</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9647861506793204</v>
+        <v>0.9646537538792979</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9856298234297227</v>
+        <v>0.9875276433791684</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2306460446788217</v>
+        <v>0.2117052266900248</v>
       </c>
       <c r="I25" t="n">
-        <v>0.06309040867101477</v>
+        <v>0.05140863840328472</v>
       </c>
       <c r="J25" t="n">
-        <v>0.133018472772912</v>
+        <v>0.1104863624247849</v>
       </c>
       <c r="K25" t="n">
-        <v>48.72100432075472</v>
+        <v>56.85567856643357</v>
       </c>
       <c r="L25" t="n">
-        <v>44.53555019245283</v>
+        <v>53.21924090909091</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Челябинск</t>
+          <t>Калининград</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4131.926315789474</v>
+        <v>5761.144104803493</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9552545051947455</v>
+        <v>0.9649069457817325</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8992518399398306</v>
+        <v>0.9554980769574002</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9637343474312238</v>
+        <v>0.9570092969314896</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9756389264163315</v>
+        <v>0.9663713563411322</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9883971471727957</v>
+        <v>0.9936454991216915</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2184439571551392</v>
+        <v>0.2278534222757574</v>
       </c>
       <c r="I26" t="n">
-        <v>0.08687517908447891</v>
+        <v>0.04281886024707735</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1353635524437698</v>
+        <v>0.1107970709976569</v>
       </c>
       <c r="K26" t="n">
-        <v>55.16710053090909</v>
+        <v>54.72073766903915</v>
       </c>
       <c r="L26" t="n">
-        <v>61.37717588727273</v>
+        <v>20.51159911921708</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ульяновск</t>
+          <t>Пермь</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4179.733333333334</v>
+        <v>3986.6796875</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9589602473925397</v>
+        <v>0.9575125152182229</v>
       </c>
       <c r="D27" t="n">
-        <v>0.94965887529639</v>
+        <v>0.8548729991464251</v>
       </c>
       <c r="E27" t="n">
-        <v>0.968952231398585</v>
+        <v>0.9350637437416682</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9611504412361787</v>
+        <v>0.9825606162978909</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9897110296820364</v>
+        <v>0.9327766973666758</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2344274192428974</v>
+        <v>0.198922852588036</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1007026277810645</v>
+        <v>0.06125558144864911</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1370108771782278</v>
+        <v>0.1172667152111024</v>
       </c>
       <c r="K27" t="n">
-        <v>54.32241853012048</v>
+        <v>58.00031938275862</v>
       </c>
       <c r="L27" t="n">
-        <v>48.41170151807229</v>
+        <v>56.22430414137931</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Чита</t>
+          <t>Барнаул</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3762.911111111111</v>
+        <v>3584.714285714286</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9821835909995692</v>
+        <v>0.9618119225953397</v>
       </c>
       <c r="D28" t="n">
-        <v>0.980436129251096</v>
+        <v>0.9348466257203721</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9869203269627445</v>
+        <v>0.9747139263148146</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9847050707787742</v>
+        <v>0.9736890167958998</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9947445883043391</v>
+        <v>0.9920429950365743</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2871794775939456</v>
+        <v>0.2579669360187042</v>
       </c>
       <c r="I28" t="n">
-        <v>0.06658668496844154</v>
+        <v>0.06102483312118659</v>
       </c>
       <c r="J28" t="n">
-        <v>0.1403552466371008</v>
+        <v>0.1184485305014237</v>
       </c>
       <c r="K28" t="n">
-        <v>52.03583832743363</v>
+        <v>53.34145224705883</v>
       </c>
       <c r="L28" t="n">
-        <v>113.4979813185841</v>
+        <v>83.74447705294118</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ижевск</t>
+          <t>Омск</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5213.757575757576</v>
+        <v>3362.811111111111</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9320572755513026</v>
+        <v>0.9629392806787805</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9258981928780242</v>
+        <v>0.8152466907680476</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9900469331197215</v>
+        <v>0.9726954641339219</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9646537538792979</v>
+        <v>0.9814661157225163</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9875276433791684</v>
+        <v>0.9673126761059034</v>
       </c>
       <c r="H29" t="n">
-        <v>0.2349405990366683</v>
+        <v>0.2205637485744479</v>
       </c>
       <c r="I29" t="n">
-        <v>0.05140863840328472</v>
+        <v>0.09907378015358301</v>
       </c>
       <c r="J29" t="n">
-        <v>0.1418804489263105</v>
+        <v>0.1186279298910913</v>
       </c>
       <c r="K29" t="n">
-        <v>56.85567856643357</v>
+        <v>54.98482156603773</v>
       </c>
       <c r="L29" t="n">
-        <v>53.21924090909091</v>
+        <v>73.35854933490566</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Калининград</t>
+          <t>Кемерово</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5761.144104803493</v>
+        <v>3869.174603174603</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9649069457817325</v>
+        <v>0.9828278534900422</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9554980769574002</v>
+        <v>0.9783234103052159</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9570092969314896</v>
+        <v>0.9918862030378047</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9663713563411322</v>
+        <v>0.9828236725842834</v>
       </c>
       <c r="G30" t="n">
-        <v>0.9936454991216915</v>
+        <v>0.9957532606877977</v>
       </c>
       <c r="H30" t="n">
-        <v>0.247984118961963</v>
+        <v>0.3177861684983343</v>
       </c>
       <c r="I30" t="n">
-        <v>0.04281886024707735</v>
+        <v>0.07870376265451108</v>
       </c>
       <c r="J30" t="n">
-        <v>0.1424399197671631</v>
+        <v>0.1212638885385448</v>
       </c>
       <c r="K30" t="n">
-        <v>54.72073766903915</v>
+        <v>55.34899745895522</v>
       </c>
       <c r="L30" t="n">
-        <v>20.51159911921708</v>
+        <v>86.11081777985073</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Петрозаводск</t>
+          <t>Тобольск</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4123.681818181818</v>
+        <v>5058.863636363636</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9440424732873276</v>
+        <v>0.9652986317769199</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9780737741625696</v>
+        <v>0.9619177682595972</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9882811373079512</v>
+        <v>0.9819995373056618</v>
       </c>
       <c r="F31" t="n">
-        <v>0.987512242401591</v>
+        <v>0.9831901002829951</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9970319814628792</v>
+        <v>0.9928387946386269</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2683248634959228</v>
+        <v>0.2902919126948355</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1060096335696689</v>
+        <v>0.1875958709052983</v>
       </c>
       <c r="J31" t="n">
-        <v>0.1424739145540508</v>
+        <v>0.1213627095239412</v>
       </c>
       <c r="K31" t="n">
-        <v>61.78167547580645</v>
+        <v>58.22035889795919</v>
       </c>
       <c r="L31" t="n">
-        <v>34.35349441129032</v>
+        <v>68.27821857142857</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Череповец</t>
+          <t>Новосибирск</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4359.309523809524</v>
+        <v>3977.447272727273</v>
       </c>
       <c r="C32" t="n">
-        <v>0.9091858036120699</v>
+        <v>0.9576789994465081</v>
       </c>
       <c r="D32" t="n">
-        <v>0.8654170197827892</v>
+        <v>0.9201096265072215</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9051915237541124</v>
+        <v>0.9054029090854322</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9335288191526564</v>
+        <v>0.9696466828184448</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9746623469301416</v>
+        <v>0.9868370838528687</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1464373563360152</v>
+        <v>0.2112771334392655</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2263761534780582</v>
+        <v>0.0212861154935136</v>
       </c>
       <c r="J32" t="n">
-        <v>0.1445795784058258</v>
+        <v>0.1237176296857649</v>
       </c>
       <c r="K32" t="n">
-        <v>59.12204149999999</v>
+        <v>55.01271715303031</v>
       </c>
       <c r="L32" t="n">
-        <v>37.92426309722222</v>
+        <v>82.93194300606061</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Пермь</t>
+          <t>Псков</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3986.6796875</v>
+        <v>5870.053571428572</v>
       </c>
       <c r="C33" t="n">
-        <v>0.9575125152182229</v>
+        <v>0.9773836358180601</v>
       </c>
       <c r="D33" t="n">
-        <v>0.8548729991464251</v>
+        <v>0.9610673667824811</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9350637437416682</v>
+        <v>0.9231807505726598</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9825606162978909</v>
+        <v>0.9895326449666655</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9327766973666758</v>
+        <v>0.9962683481798553</v>
       </c>
       <c r="H33" t="n">
-        <v>0.226528508095531</v>
+        <v>0.2842950332028773</v>
       </c>
       <c r="I33" t="n">
-        <v>0.06125558144864911</v>
+        <v>0.1865314108110565</v>
       </c>
       <c r="J33" t="n">
-        <v>0.1493054888932038</v>
+        <v>0.1292939298016784</v>
       </c>
       <c r="K33" t="n">
-        <v>58.00031938275862</v>
+        <v>57.81487988461539</v>
       </c>
       <c r="L33" t="n">
-        <v>56.22430414137931</v>
+        <v>28.33200775641026</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Астрахань</t>
+          <t>Томск</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3440.238805970149</v>
+        <v>3757.434210526316</v>
       </c>
       <c r="C34" t="n">
-        <v>0.9784383109912644</v>
+        <v>0.9814168464835591</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9315906499349267</v>
+        <v>0.9474433314549505</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9836314194782991</v>
+        <v>0.9711280338166176</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9579361924183152</v>
+        <v>0.9847234133311041</v>
       </c>
       <c r="G34" t="n">
-        <v>0.994871644320056</v>
+        <v>0.9908600486584006</v>
       </c>
       <c r="H34" t="n">
-        <v>0.2813580319899452</v>
+        <v>0.3171209198799234</v>
       </c>
       <c r="I34" t="n">
-        <v>0.07471430287303056</v>
+        <v>0.1502091368758373</v>
       </c>
       <c r="J34" t="n">
-        <v>0.151185090618497</v>
+        <v>0.1299431022506615</v>
       </c>
       <c r="K34" t="n">
-        <v>46.35151272058823</v>
+        <v>56.47955309271524</v>
       </c>
       <c r="L34" t="n">
-        <v>48.0335039632353</v>
+        <v>84.97116295364239</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Саратов</t>
+          <t>Сыктывкар</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4217.022727272727</v>
+        <v>3332.96</v>
       </c>
       <c r="C35" t="n">
-        <v>0.9740909092296519</v>
+        <v>0.9708893709768682</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9703381507659136</v>
+        <v>0.9600634386722775</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9746769514757834</v>
+        <v>0.7905832337173756</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9735788414714274</v>
+        <v>0.980076055441561</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9906619954981383</v>
+        <v>0.9904389154552714</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2945881174385239</v>
+        <v>0.1920568740225903</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1123932398659774</v>
+        <v>0.1391353057019446</v>
       </c>
       <c r="J35" t="n">
-        <v>0.1525710353264962</v>
+        <v>0.1350720268716439</v>
       </c>
       <c r="K35" t="n">
-        <v>51.54124806976744</v>
+        <v>61.6742125</v>
       </c>
       <c r="L35" t="n">
-        <v>46.02896238372093</v>
+        <v>50.819564875</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Красноярск</t>
+          <t>Орск</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3864.569696969697</v>
+        <v>4675.083333333333</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8835842428558431</v>
+        <v>0.9901330597430009</v>
       </c>
       <c r="D36" t="n">
-        <v>0.8467747437195878</v>
+        <v>0.9859740778047091</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9349630639095432</v>
+        <v>0.9855724775057988</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9697378433864328</v>
+        <v>0.9892645722383611</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9275243433077786</v>
+        <v>0.998272878374614</v>
       </c>
       <c r="H36" t="n">
-        <v>0.2101003176609448</v>
+        <v>0.3677911320577529</v>
       </c>
       <c r="I36" t="n">
-        <v>0.04022963829323167</v>
+        <v>0.1551813953336285</v>
       </c>
       <c r="J36" t="n">
-        <v>0.167206027007734</v>
+        <v>0.1354548286910951</v>
       </c>
       <c r="K36" t="n">
-        <v>56.02923273294347</v>
+        <v>51.23977365384615</v>
       </c>
       <c r="L36" t="n">
-        <v>92.88013770565303</v>
+        <v>58.49201876923077</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Оренбург</t>
+          <t>Новокузнецк</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3529.526315789474</v>
+        <v>3965.836734693878</v>
       </c>
       <c r="C37" t="n">
-        <v>0.9614093962077501</v>
+        <v>0.9573833520516564</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9577813943380641</v>
+        <v>0.9426529956416373</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8141286374521483</v>
+        <v>0.9694972521263953</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9641856105220762</v>
+        <v>0.9531913880432364</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9901963258041365</v>
+        <v>0.9942867432620857</v>
       </c>
       <c r="H37" t="n">
-        <v>0.2465512009614503</v>
+        <v>0.2905731380178082</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1082315546882008</v>
+        <v>0.09132681733571003</v>
       </c>
       <c r="J37" t="n">
-        <v>0.1787288986295499</v>
+        <v>0.1354908308333995</v>
       </c>
       <c r="K37" t="n">
-        <v>51.7864696936937</v>
+        <v>53.76131239516129</v>
       </c>
       <c r="L37" t="n">
-        <v>55.12567940540541</v>
+        <v>87.14451374193548</v>
       </c>
     </row>
     <row r="38">
@@ -1955,13 +1955,13 @@
         <v>0.9973661691628328</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1887646700252638</v>
+        <v>0.1374090293692</v>
       </c>
       <c r="I38" t="n">
         <v>0.03454753210319957</v>
       </c>
       <c r="J38" t="n">
-        <v>0.1818880275701055</v>
+        <v>0.1455506427445174</v>
       </c>
       <c r="K38" t="n">
         <v>68.95859641317365</v>
@@ -1973,121 +1973,121 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Псков</t>
+          <t>Оренбург</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>5870.053571428572</v>
+        <v>3497.857142857143</v>
       </c>
       <c r="C39" t="n">
-        <v>0.9773836358180601</v>
+        <v>0.9614093962077501</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9610673667824811</v>
+        <v>0.9577813943380641</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9231807505726598</v>
+        <v>0.8141286374521483</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9895326449666655</v>
+        <v>0.9641856105220762</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9962683481798553</v>
+        <v>0.9901963258041365</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3440746982166978</v>
+        <v>0.2600905313011303</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1865314108110565</v>
+        <v>0.1078019014431335</v>
       </c>
       <c r="J39" t="n">
-        <v>0.1840264857280472</v>
+        <v>0.1586771508488961</v>
       </c>
       <c r="K39" t="n">
-        <v>57.81487988461539</v>
+        <v>51.7864696936937</v>
       </c>
       <c r="L39" t="n">
-        <v>28.33200775641026</v>
+        <v>55.12567940540541</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Сыктывкар</t>
+          <t>Элиста</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3332.96</v>
+        <v>4339.68</v>
       </c>
       <c r="C40" t="n">
-        <v>0.9708893709768682</v>
+        <v>0.9837150064719219</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9600634386722775</v>
+        <v>0.9801936996486886</v>
       </c>
       <c r="E40" t="n">
-        <v>0.7905832337173756</v>
+        <v>0.8574410697873854</v>
       </c>
       <c r="F40" t="n">
-        <v>0.980076055441561</v>
+        <v>0.9816001579886884</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9904389154552714</v>
+        <v>0.9896771696014739</v>
       </c>
       <c r="H40" t="n">
-        <v>0.2923111561647376</v>
+        <v>0.3789285253545044</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1391353057019446</v>
+        <v>0.1633694323824786</v>
       </c>
       <c r="J40" t="n">
-        <v>0.1983895984164477</v>
+        <v>0.1754388021613606</v>
       </c>
       <c r="K40" t="n">
-        <v>61.6742125</v>
+        <v>46.30705727777777</v>
       </c>
       <c r="L40" t="n">
-        <v>50.819564875</v>
+        <v>44.27788655555556</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Махачкала</t>
+          <t>Ставрополь</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>5000.786764705882</v>
+        <v>3348.3125</v>
       </c>
       <c r="C41" t="n">
-        <v>0.8525091841755768</v>
+        <v>0.9846350405367271</v>
       </c>
       <c r="D41" t="n">
-        <v>0.8401191751656595</v>
+        <v>0.9890403468901975</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9741721658513738</v>
+        <v>0.9869248749039411</v>
       </c>
       <c r="F41" t="n">
-        <v>0.938169996389365</v>
+        <v>0.9858796453006357</v>
       </c>
       <c r="G41" t="n">
-        <v>0.9824492343076351</v>
+        <v>0.9958666714965215</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2660926990074046</v>
+        <v>0.501827605277879</v>
       </c>
       <c r="I41" t="n">
-        <v>0.09664198006456383</v>
+        <v>0.05680268038603788</v>
       </c>
       <c r="J41" t="n">
-        <v>0.1984800824278515</v>
+        <v>0.1826264381728855</v>
       </c>
       <c r="K41" t="n">
-        <v>42.9738446146789</v>
+        <v>45.04022625806451</v>
       </c>
       <c r="L41" t="n">
-        <v>47.52243708715596</v>
+        <v>41.94070197849462</v>
       </c>
     </row>
     <row r="42">
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3693.67217630854</v>
+        <v>3694.439226519337</v>
       </c>
       <c r="C42" t="n">
         <v>0.9685970318391023</v>
@@ -2115,13 +2115,13 @@
         <v>0.9886601229116374</v>
       </c>
       <c r="H42" t="n">
-        <v>0.387007237138666</v>
+        <v>0.4619200209205742</v>
       </c>
       <c r="I42" t="n">
-        <v>0.03240080589869483</v>
+        <v>0.03246783144504514</v>
       </c>
       <c r="J42" t="n">
-        <v>0.199214848769798</v>
+        <v>0.1859844715417802</v>
       </c>
       <c r="K42" t="n">
         <v>45.058334</v>
@@ -2133,881 +2133,881 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Братск</t>
+          <t>Чита</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3697.9</v>
+        <v>3762.911111111111</v>
       </c>
       <c r="C43" t="n">
-        <v>0.9824972865927867</v>
+        <v>0.9821835909995692</v>
       </c>
       <c r="D43" t="n">
-        <v>0.9949265254024324</v>
+        <v>0.980436129251096</v>
       </c>
       <c r="E43" t="n">
-        <v>0.999604556045127</v>
+        <v>0.9869203269627445</v>
       </c>
       <c r="F43" t="n">
-        <v>0.981866377136547</v>
+        <v>0.9847050707787742</v>
       </c>
       <c r="G43" t="n">
-        <v>0.999119744251533</v>
+        <v>0.9947445883043391</v>
       </c>
       <c r="H43" t="n">
-        <v>0.4310121807019506</v>
+        <v>0.5081700225522217</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3105876405098693</v>
+        <v>0.06658668496844154</v>
       </c>
       <c r="J43" t="n">
-        <v>0.1992368851387016</v>
+        <v>0.1867740841635201</v>
       </c>
       <c r="K43" t="n">
-        <v>56.18498009523809</v>
+        <v>52.03583832743363</v>
       </c>
       <c r="L43" t="n">
-        <v>101.6566364761905</v>
+        <v>113.4979813185841</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Сочи</t>
+          <t>Красноярск</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>5506.083948339483</v>
+        <v>3872.451219512195</v>
       </c>
       <c r="C44" t="n">
-        <v>0.9134669581614204</v>
+        <v>0.8835842428558431</v>
       </c>
       <c r="D44" t="n">
-        <v>0.884078736896061</v>
+        <v>0.8467747437195878</v>
       </c>
       <c r="E44" t="n">
-        <v>0.8749740570573415</v>
+        <v>0.9349630639095432</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9225424476620222</v>
+        <v>0.9697378433864328</v>
       </c>
       <c r="G44" t="n">
-        <v>0.9757958660475599</v>
+        <v>0.9275243433077786</v>
       </c>
       <c r="H44" t="n">
-        <v>0.256981932457635</v>
+        <v>0.3301959383445329</v>
       </c>
       <c r="I44" t="n">
-        <v>0.01048207577756948</v>
+        <v>0.04006249197547137</v>
       </c>
       <c r="J44" t="n">
-        <v>0.1995997557136601</v>
+        <v>0.1870285062740595</v>
       </c>
       <c r="K44" t="n">
-        <v>43.57957087337662</v>
+        <v>56.02923273294347</v>
       </c>
       <c r="L44" t="n">
-        <v>39.75287353043831</v>
+        <v>92.88013770565303</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Минеральные Воды</t>
+          <t>Владикавказ</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4024.6</v>
+        <v>5034.131147540984</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8881548250272128</v>
+        <v>0.9697874436441855</v>
       </c>
       <c r="D45" t="n">
-        <v>0.8375312490181114</v>
+        <v>0.9887184610931057</v>
       </c>
       <c r="E45" t="n">
-        <v>0.8750959221113165</v>
+        <v>0.9609810043210857</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9170481295527585</v>
+        <v>0.982471077855754</v>
       </c>
       <c r="G45" t="n">
-        <v>0.9705717606902701</v>
+        <v>0.9987419707948038</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2547397592704996</v>
+        <v>0.4862281472746664</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1852318066861665</v>
+        <v>0.1392931088855753</v>
       </c>
       <c r="J45" t="n">
-        <v>0.2126627572050463</v>
+        <v>0.1888688186554204</v>
       </c>
       <c r="K45" t="n">
-        <v>44.20459886956522</v>
+        <v>43.03523083809524</v>
       </c>
       <c r="L45" t="n">
-        <v>43.12653991304348</v>
+        <v>44.66105326666666</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Норильск</t>
+          <t>Сочи</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>13281.75</v>
+        <v>5499.308973172988</v>
       </c>
       <c r="C46" t="n">
-        <v>0.9858129571229453</v>
+        <v>0.9134669581614204</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9976525285118737</v>
+        <v>0.884078736896061</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>0.8749740570573415</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9829273585044247</v>
+        <v>0.9225424476620222</v>
       </c>
       <c r="G46" t="n">
-        <v>0.9996123178898466</v>
+        <v>0.9757958660475599</v>
       </c>
       <c r="H46" t="n">
-        <v>0.4751849817420942</v>
+        <v>0.3110649195849929</v>
       </c>
       <c r="I46" t="n">
-        <v>0.4155540384316216</v>
+        <v>0.01044523054085902</v>
       </c>
       <c r="J46" t="n">
-        <v>0.2170625856935133</v>
+        <v>0.1922897780911983</v>
       </c>
       <c r="K46" t="n">
-        <v>69.35556087671233</v>
+        <v>43.57957087337662</v>
       </c>
       <c r="L46" t="n">
-        <v>88.19681464383561</v>
+        <v>39.75287353043831</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Владикавказ</t>
+          <t>Нальчик</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>5034.131147540984</v>
+        <v>4378.133333333333</v>
       </c>
       <c r="C47" t="n">
-        <v>0.9697874436441855</v>
+        <v>0.9762690372527054</v>
       </c>
       <c r="D47" t="n">
-        <v>0.9887184610931057</v>
+        <v>0.9755299680699883</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9609810043210857</v>
+        <v>0.8856840353989809</v>
       </c>
       <c r="F47" t="n">
-        <v>0.982471077855754</v>
+        <v>0.95986253810296</v>
       </c>
       <c r="G47" t="n">
-        <v>0.9987419707948038</v>
+        <v>0.9937946092704377</v>
       </c>
       <c r="H47" t="n">
-        <v>0.4495706657328854</v>
+        <v>0.4289333021719349</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1392931088855753</v>
+        <v>0.242761838269459</v>
       </c>
       <c r="J47" t="n">
-        <v>0.2213623415045033</v>
+        <v>0.1926635639154079</v>
       </c>
       <c r="K47" t="n">
-        <v>43.03523083809524</v>
+        <v>43.47520687234042</v>
       </c>
       <c r="L47" t="n">
-        <v>44.66105326666666</v>
+        <v>43.59387540425531</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Иркутск</t>
+          <t>Махачкала</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3950.577540106952</v>
+        <v>5000.786764705882</v>
       </c>
       <c r="C48" t="n">
-        <v>0.9413660433718316</v>
+        <v>0.8525091841755768</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9203495000895475</v>
+        <v>0.8401191751656595</v>
       </c>
       <c r="E48" t="n">
-        <v>0.7265276293704855</v>
+        <v>0.9741721658513738</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9804045039561693</v>
+        <v>0.938169996389365</v>
       </c>
       <c r="G48" t="n">
-        <v>0.9839220289229417</v>
+        <v>0.9824492343076351</v>
       </c>
       <c r="H48" t="n">
-        <v>0.2860192400965731</v>
+        <v>0.3283500087211096</v>
       </c>
       <c r="I48" t="n">
-        <v>0.08543250223610228</v>
+        <v>0.09664198006456383</v>
       </c>
       <c r="J48" t="n">
-        <v>0.2248935198804984</v>
+        <v>0.1930382978297708</v>
       </c>
       <c r="K48" t="n">
-        <v>52.27154337871287</v>
+        <v>42.9738446146789</v>
       </c>
       <c r="L48" t="n">
-        <v>104.3046311980198</v>
+        <v>47.52243708715596</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ставрополь</t>
+          <t>Минеральные Воды</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3348.3125</v>
+        <v>4024.6</v>
       </c>
       <c r="C49" t="n">
-        <v>0.9846350405367271</v>
+        <v>0.8881548250272128</v>
       </c>
       <c r="D49" t="n">
-        <v>0.9890403468901975</v>
+        <v>0.8375312490181114</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9869248749039411</v>
+        <v>0.8750959221113165</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9858796453006357</v>
+        <v>0.9170481295527585</v>
       </c>
       <c r="G49" t="n">
-        <v>0.9958666714965215</v>
+        <v>0.9705717606902701</v>
       </c>
       <c r="H49" t="n">
-        <v>0.4961402207348549</v>
+        <v>0.297622691829439</v>
       </c>
       <c r="I49" t="n">
-        <v>0.05680268038603788</v>
+        <v>0.1852318066861665</v>
       </c>
       <c r="J49" t="n">
-        <v>0.2303067495017428</v>
+        <v>0.2017689783480358</v>
       </c>
       <c r="K49" t="n">
-        <v>45.04022625806451</v>
+        <v>44.20459886956522</v>
       </c>
       <c r="L49" t="n">
-        <v>41.94070197849462</v>
+        <v>43.12653991304348</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Орск</t>
+          <t>Братск</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4675.083333333333</v>
+        <v>3697.9</v>
       </c>
       <c r="C50" t="n">
-        <v>0.9901330597430009</v>
+        <v>0.9824972865927867</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9859740778047091</v>
+        <v>0.9949265254024324</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9855724775057988</v>
+        <v>0.999604556045127</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9892645722383611</v>
+        <v>0.981866377136547</v>
       </c>
       <c r="G50" t="n">
-        <v>0.998272878374614</v>
+        <v>0.999119744251533</v>
       </c>
       <c r="H50" t="n">
-        <v>0.5185977018872185</v>
+        <v>0.5767863925782761</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1551813953336285</v>
+        <v>0.3105876405098693</v>
       </c>
       <c r="J50" t="n">
-        <v>0.2385888326218353</v>
+        <v>0.2056988991064572</v>
       </c>
       <c r="K50" t="n">
-        <v>51.23977365384615</v>
+        <v>56.18498009523809</v>
       </c>
       <c r="L50" t="n">
-        <v>58.49201876923077</v>
+        <v>101.6566364761905</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Якутск</t>
+          <t>Магнитогорск</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>5039.971428571429</v>
+        <v>3866.51724137931</v>
       </c>
       <c r="C51" t="n">
-        <v>0.9560973194173357</v>
+        <v>0.9584843499120236</v>
       </c>
       <c r="D51" t="n">
-        <v>0.8697154712751538</v>
+        <v>0.9419979900701169</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9769504712366565</v>
+        <v>0.9061126309262539</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9862845206968801</v>
+        <v>0.960692250823123</v>
       </c>
       <c r="G51" t="n">
-        <v>0.9975397171459859</v>
+        <v>0.9865939473074152</v>
       </c>
       <c r="H51" t="n">
-        <v>0.4641734116168593</v>
+        <v>0.4811217734589172</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1210614628427784</v>
+        <v>0.1794922190657843</v>
       </c>
       <c r="J51" t="n">
-        <v>0.2412448547718634</v>
+        <v>0.2143076522887117</v>
       </c>
       <c r="K51" t="n">
-        <v>62.028693</v>
+        <v>53.39839404123711</v>
       </c>
       <c r="L51" t="n">
-        <v>129.730531125</v>
+        <v>58.98401029896907</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Нальчик</t>
+          <t>Норильск</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4378.133333333333</v>
+        <v>13281.75</v>
       </c>
       <c r="C52" t="n">
-        <v>0.9762690372527054</v>
+        <v>0.9858129571229453</v>
       </c>
       <c r="D52" t="n">
-        <v>0.9755299680699883</v>
+        <v>0.9976525285118737</v>
       </c>
       <c r="E52" t="n">
-        <v>0.8856840353989809</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>0.95986253810296</v>
+        <v>0.9829273585044247</v>
       </c>
       <c r="G52" t="n">
-        <v>0.9937946092704377</v>
+        <v>0.9996123178898466</v>
       </c>
       <c r="H52" t="n">
-        <v>0.451149167069463</v>
+        <v>0.6685224563116835</v>
       </c>
       <c r="I52" t="n">
-        <v>0.242761838269459</v>
+        <v>0.4155540384316216</v>
       </c>
       <c r="J52" t="n">
-        <v>0.2453318746875137</v>
+        <v>0.2352788288729643</v>
       </c>
       <c r="K52" t="n">
-        <v>43.47520687234042</v>
+        <v>69.35556087671233</v>
       </c>
       <c r="L52" t="n">
-        <v>43.59387540425531</v>
+        <v>88.19681464383561</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Элиста</t>
+          <t>Грозный</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4339.68</v>
+        <v>4809.787878787879</v>
       </c>
       <c r="C53" t="n">
-        <v>0.9837150064719219</v>
+        <v>0.987313967201933</v>
       </c>
       <c r="D53" t="n">
-        <v>0.9801936996486886</v>
+        <v>0.9911581221827264</v>
       </c>
       <c r="E53" t="n">
-        <v>0.8574410697873854</v>
+        <v>0.8172096218628665</v>
       </c>
       <c r="F53" t="n">
-        <v>0.9816001579886884</v>
+        <v>0.9850458108737845</v>
       </c>
       <c r="G53" t="n">
-        <v>0.9896771696014739</v>
+        <v>0.9966865641493765</v>
       </c>
       <c r="H53" t="n">
-        <v>0.4837404101319802</v>
+        <v>0.5375884263056844</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1633694323824786</v>
+        <v>0.1169330746218671</v>
       </c>
       <c r="J53" t="n">
-        <v>0.2594488839989004</v>
+        <v>0.2363580140442336</v>
       </c>
       <c r="K53" t="n">
-        <v>46.30705727777777</v>
+        <v>43.31621724390244</v>
       </c>
       <c r="L53" t="n">
-        <v>44.27788655555556</v>
+        <v>45.69695185365853</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Благовещенск</t>
+          <t>Иркутск</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4524.935483870968</v>
+        <v>3950.577540106952</v>
       </c>
       <c r="C54" t="n">
-        <v>0.9521741158988773</v>
+        <v>0.9413660433718316</v>
       </c>
       <c r="D54" t="n">
-        <v>0.936069194449889</v>
+        <v>0.9203495000895475</v>
       </c>
       <c r="E54" t="n">
-        <v>0.9301984425204214</v>
+        <v>0.7265276293704855</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9299791122292904</v>
+        <v>0.9804045039561693</v>
       </c>
       <c r="G54" t="n">
-        <v>0.994759315285408</v>
+        <v>0.9839220289229417</v>
       </c>
       <c r="H54" t="n">
-        <v>0.4826847364919005</v>
+        <v>0.435853475434939</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1340028824228011</v>
+        <v>0.08543250223610228</v>
       </c>
       <c r="J54" t="n">
-        <v>0.2660772629135187</v>
+        <v>0.2472352358858855</v>
       </c>
       <c r="K54" t="n">
-        <v>50.2734886122449</v>
+        <v>52.27154337871287</v>
       </c>
       <c r="L54" t="n">
-        <v>127.5312437142857</v>
+        <v>104.3046311980198</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Магнитогорск</t>
+          <t>Якутск</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3846.833333333333</v>
+        <v>5039.971428571429</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9584843499120236</v>
+        <v>0.9560973194173357</v>
       </c>
       <c r="D55" t="n">
-        <v>0.9419979900701169</v>
+        <v>0.8697154712751538</v>
       </c>
       <c r="E55" t="n">
-        <v>0.9061126309262539</v>
+        <v>0.9769504712366565</v>
       </c>
       <c r="F55" t="n">
-        <v>0.960692250823123</v>
+        <v>0.9862845206968801</v>
       </c>
       <c r="G55" t="n">
-        <v>0.9865939473074152</v>
+        <v>0.9975397171459859</v>
       </c>
       <c r="H55" t="n">
-        <v>0.4913486863617472</v>
+        <v>0.6790835639107509</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1780662616079623</v>
+        <v>0.1210614628427784</v>
       </c>
       <c r="J55" t="n">
-        <v>0.2669196713118486</v>
+        <v>0.2678969653901006</v>
       </c>
       <c r="K55" t="n">
-        <v>53.39839404123711</v>
+        <v>62.028693</v>
       </c>
       <c r="L55" t="n">
-        <v>58.98401029896907</v>
+        <v>129.730531125</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Владивосток</t>
+          <t>Благовещенск</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>5452.831632653061</v>
+        <v>4524.935483870968</v>
       </c>
       <c r="C56" t="n">
-        <v>0.9782966096867975</v>
+        <v>0.9521741158988773</v>
       </c>
       <c r="D56" t="n">
-        <v>0.9709249252906753</v>
+        <v>0.936069194449889</v>
       </c>
       <c r="E56" t="n">
-        <v>0.9726722378724121</v>
+        <v>0.9301984425204214</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9794896686324287</v>
+        <v>0.9299791122292904</v>
       </c>
       <c r="G56" t="n">
-        <v>0.9954775555406947</v>
+        <v>0.994759315285408</v>
       </c>
       <c r="H56" t="n">
-        <v>0.5868105959443034</v>
+        <v>0.6583065001455304</v>
       </c>
       <c r="I56" t="n">
-        <v>0.03433793893824245</v>
+        <v>0.1340028824228011</v>
       </c>
       <c r="J56" t="n">
-        <v>0.279118764490528</v>
+        <v>0.2775201889065629</v>
       </c>
       <c r="K56" t="n">
-        <v>43.13194217302799</v>
+        <v>50.2734886122449</v>
       </c>
       <c r="L56" t="n">
-        <v>131.9208271246819</v>
+        <v>127.5312437142857</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Грозный</t>
+          <t>Владивосток</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4809.787878787879</v>
+        <v>5444.149484536082</v>
       </c>
       <c r="C57" t="n">
-        <v>0.987313967201933</v>
+        <v>0.9782966096867975</v>
       </c>
       <c r="D57" t="n">
-        <v>0.9911581221827264</v>
+        <v>0.9709249252906753</v>
       </c>
       <c r="E57" t="n">
-        <v>0.8172096218628665</v>
+        <v>0.9726722378724121</v>
       </c>
       <c r="F57" t="n">
-        <v>0.9850458108737845</v>
+        <v>0.9794896686324287</v>
       </c>
       <c r="G57" t="n">
-        <v>0.9966865641493765</v>
+        <v>0.9954775555406947</v>
       </c>
       <c r="H57" t="n">
-        <v>0.5254223929121107</v>
+        <v>0.7715275954888234</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1169330746218671</v>
+        <v>0.0523659456649746</v>
       </c>
       <c r="J57" t="n">
-        <v>0.2847638019816296</v>
+        <v>0.2832414847412346</v>
       </c>
       <c r="K57" t="n">
-        <v>43.31621724390244</v>
+        <v>43.13194217302799</v>
       </c>
       <c r="L57" t="n">
-        <v>45.69695185365853</v>
+        <v>131.9208271246819</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Хабаровск</t>
+          <t>Анапа</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4403.1875</v>
+        <v>6421.603411513859</v>
       </c>
       <c r="C58" t="n">
-        <v>0.9287171649232053</v>
+        <v>0.9271161123117518</v>
       </c>
       <c r="D58" t="n">
-        <v>0.9295967399700714</v>
+        <v>0.891244494338463</v>
       </c>
       <c r="E58" t="n">
-        <v>0.9797011919274214</v>
+        <v>0.8965903897315294</v>
       </c>
       <c r="F58" t="n">
-        <v>0.9591886338787106</v>
+        <v>0.9400985435534048</v>
       </c>
       <c r="G58" t="n">
-        <v>0.9838147245223614</v>
+        <v>0.9749362101068868</v>
       </c>
       <c r="H58" t="n">
-        <v>0.5764385892875992</v>
+        <v>0.6611499594476323</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1072646105456405</v>
+        <v>0.01623125566243791</v>
       </c>
       <c r="J58" t="n">
-        <v>0.2963984815660209</v>
+        <v>0.297409682742074</v>
       </c>
       <c r="K58" t="n">
-        <v>48.478464775</v>
+        <v>44.93442789230769</v>
       </c>
       <c r="L58" t="n">
-        <v>135.0810953125</v>
+        <v>37.29969087582417</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Южно-Сахалинск</t>
+          <t>Магадан</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>6026.934782608696</v>
+        <v>7063</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8768114006565895</v>
+        <v>0.9955442576002288</v>
       </c>
       <c r="D59" t="n">
-        <v>0.9359293950080657</v>
+        <v>0.996497237645053</v>
       </c>
       <c r="E59" t="n">
-        <v>0.9621676791431758</v>
+        <v>0.9974580054978246</v>
       </c>
       <c r="F59" t="n">
-        <v>0.9807490920504253</v>
+        <v>0.9940619494352145</v>
       </c>
       <c r="G59" t="n">
-        <v>0.9969605974294276</v>
+        <v>0.99962209640428</v>
       </c>
       <c r="H59" t="n">
-        <v>0.5475342880747067</v>
+        <v>0.8685037779149177</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1473025940000444</v>
+        <v>0.1997722905805808</v>
       </c>
       <c r="J59" t="n">
-        <v>0.2978290240451089</v>
+        <v>0.2988862705137481</v>
       </c>
       <c r="K59" t="n">
-        <v>46.93392028</v>
+        <v>59.6085957826087</v>
       </c>
       <c r="L59" t="n">
-        <v>142.7446941</v>
+        <v>150.799767826087</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Улан-Удэ</t>
+          <t>Хабаровск</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3768.30985915493</v>
+        <v>4404.178947368421</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7924362947950625</v>
+        <v>0.9287171649232053</v>
       </c>
       <c r="D60" t="n">
-        <v>0.6199741832791631</v>
+        <v>0.9295967399700714</v>
       </c>
       <c r="E60" t="n">
-        <v>0.7624670878354982</v>
+        <v>0.9797011919274214</v>
       </c>
       <c r="F60" t="n">
-        <v>0.9443726028500559</v>
+        <v>0.9591886338787106</v>
       </c>
       <c r="G60" t="n">
-        <v>0.9873238449586127</v>
+        <v>0.9838147245223614</v>
       </c>
       <c r="H60" t="n">
-        <v>0.2817369227565458</v>
+        <v>0.7566961667198797</v>
       </c>
       <c r="I60" t="n">
-        <v>0.07654949429695447</v>
+        <v>0.1056415640431052</v>
       </c>
       <c r="J60" t="n">
-        <v>0.3008257999714262</v>
+        <v>0.3000421989642364</v>
       </c>
       <c r="K60" t="n">
-        <v>51.83094390510949</v>
+        <v>48.478464775</v>
       </c>
       <c r="L60" t="n">
-        <v>107.6049323138686</v>
+        <v>135.0810953125</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Магадан</t>
+          <t>Южно-Сахалинск</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>7063</v>
+        <v>6026.934782608696</v>
       </c>
       <c r="C61" t="n">
-        <v>0.9955442576002288</v>
+        <v>0.8768114006565895</v>
       </c>
       <c r="D61" t="n">
-        <v>0.996497237645053</v>
+        <v>0.9359293950080657</v>
       </c>
       <c r="E61" t="n">
-        <v>0.9974580054978246</v>
+        <v>0.9621676791431758</v>
       </c>
       <c r="F61" t="n">
-        <v>0.9940619494352145</v>
+        <v>0.9807490920504253</v>
       </c>
       <c r="G61" t="n">
-        <v>0.99962209640428</v>
+        <v>0.9969605974294276</v>
       </c>
       <c r="H61" t="n">
-        <v>0.6894238925100461</v>
+        <v>0.7239759100933369</v>
       </c>
       <c r="I61" t="n">
-        <v>0.1997722905805808</v>
+        <v>0.1473025940000444</v>
       </c>
       <c r="J61" t="n">
-        <v>0.3069414987270964</v>
+        <v>0.3030657467239725</v>
       </c>
       <c r="K61" t="n">
-        <v>59.6085957826087</v>
+        <v>46.93392028</v>
       </c>
       <c r="L61" t="n">
-        <v>150.799767826087</v>
+        <v>142.7446941</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Анапа</t>
+          <t>Петропавловск-Камчатский</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>6426.660297239915</v>
+        <v>7271.142857142857</v>
       </c>
       <c r="C62" t="n">
-        <v>0.9271161123117518</v>
+        <v>0.9690487577278898</v>
       </c>
       <c r="D62" t="n">
-        <v>0.891244494338463</v>
+        <v>0.9682951727487853</v>
       </c>
       <c r="E62" t="n">
-        <v>0.8965903897315294</v>
+        <v>0.9494194790736691</v>
       </c>
       <c r="F62" t="n">
-        <v>0.9400985435534048</v>
+        <v>0.9591990588834239</v>
       </c>
       <c r="G62" t="n">
-        <v>0.9749362101068868</v>
+        <v>0.9919994721313027</v>
       </c>
       <c r="H62" t="n">
-        <v>0.5653402520308271</v>
+        <v>0.8819670938929628</v>
       </c>
       <c r="I62" t="n">
-        <v>0.01618481128853154</v>
+        <v>0.07605659727757094</v>
       </c>
       <c r="J62" t="n">
-        <v>0.321368407423443</v>
+        <v>0.3338625793187288</v>
       </c>
       <c r="K62" t="n">
-        <v>44.93442789230769</v>
+        <v>53.05938700671141</v>
       </c>
       <c r="L62" t="n">
-        <v>37.29969087582417</v>
+        <v>158.5600306040268</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Абакан</t>
+          <t>Улан-Удэ</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>4189.833333333333</v>
+        <v>3768.30985915493</v>
       </c>
       <c r="C63" t="n">
-        <v>0.7859654934430211</v>
+        <v>0.7924362947950625</v>
       </c>
       <c r="D63" t="n">
-        <v>0.835842459508378</v>
+        <v>0.6199741832791631</v>
       </c>
       <c r="E63" t="n">
-        <v>0.8783648606959352</v>
+        <v>0.7624670878354982</v>
       </c>
       <c r="F63" t="n">
-        <v>0.5951691433478243</v>
+        <v>0.9443726028500559</v>
       </c>
       <c r="G63" t="n">
-        <v>0.9571355241661988</v>
+        <v>0.9873238449586127</v>
       </c>
       <c r="H63" t="n">
-        <v>0.2971339255819553</v>
+        <v>0.4722112251711306</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2325812712847873</v>
+        <v>0.07654949429695447</v>
       </c>
       <c r="J63" t="n">
-        <v>0.3279311037395519</v>
+        <v>0.3374133705167304</v>
       </c>
       <c r="K63" t="n">
-        <v>53.72504284444445</v>
+        <v>51.83094390510949</v>
       </c>
       <c r="L63" t="n">
-        <v>91.43001235555556</v>
+        <v>107.6049323138686</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Петропавловск-Камчатский</t>
+          <t>Абакан</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>7271.142857142857</v>
+        <v>4189.833333333333</v>
       </c>
       <c r="C64" t="n">
-        <v>0.9690487577278898</v>
+        <v>0.7859654934430211</v>
       </c>
       <c r="D64" t="n">
-        <v>0.9682951727487853</v>
+        <v>0.835842459508378</v>
       </c>
       <c r="E64" t="n">
-        <v>0.9494194790736691</v>
+        <v>0.8783648606959352</v>
       </c>
       <c r="F64" t="n">
-        <v>0.9591990588834239</v>
+        <v>0.5951691433478243</v>
       </c>
       <c r="G64" t="n">
-        <v>0.9919994721313027</v>
+        <v>0.9571355241661988</v>
       </c>
       <c r="H64" t="n">
-        <v>0.6770159572874146</v>
+        <v>0.4610333189408314</v>
       </c>
       <c r="I64" t="n">
-        <v>0.07605659727757094</v>
+        <v>0.2325812712847873</v>
       </c>
       <c r="J64" t="n">
-        <v>0.3318807886015838</v>
+        <v>0.3539435049233743</v>
       </c>
       <c r="K64" t="n">
-        <v>53.05938700671141</v>
+        <v>53.72504284444445</v>
       </c>
       <c r="L64" t="n">
-        <v>158.5600306040268</v>
+        <v>91.43001235555556</v>
       </c>
     </row>
     <row r="65">
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>4069.0625</v>
+        <v>4070.559748427673</v>
       </c>
       <c r="C73" t="n">
         <v>0.9782114499317685</v>
@@ -3312,7 +3312,7 @@
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="n">
-        <v>0.04283815207367336</v>
+        <v>0.04293118713138519</v>
       </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="n">
@@ -3337,7 +3337,7 @@
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>0.2045845276022572</v>
+        <v>0.3353850300925455</v>
       </c>
       <c r="I74" t="n">
         <v>0.125536011114221</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>4230.848484848485</v>
+        <v>4252.90625</v>
       </c>
       <c r="C82" t="n">
         <v>0.9720055260619719</v>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="n">
-        <v>0.1376015698097832</v>
+        <v>0.1406655978043406</v>
       </c>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="n">
@@ -3725,7 +3725,7 @@
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>0.4250722659112715</v>
+        <v>0.3121965841412165</v>
       </c>
       <c r="I85" t="n">
         <v>0.4473774802070397</v>
@@ -3889,26 +3889,26 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>4169.424657534247</v>
+        <v>4177.263888888889</v>
       </c>
       <c r="C90" t="n">
-        <v>0.9210790621885647</v>
+        <v>0.920175117490905</v>
       </c>
       <c r="D90" t="n">
-        <v>0.869907313401988</v>
+        <v>0.8685354054675285</v>
       </c>
       <c r="E90" t="n">
-        <v>0.9037778218892377</v>
+        <v>0.9024754848498383</v>
       </c>
       <c r="F90" t="n">
-        <v>0.9246643696581176</v>
+        <v>0.9238195664161055</v>
       </c>
       <c r="G90" t="n">
-        <v>0.9913910588150634</v>
+        <v>0.9913834440626231</v>
       </c>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="n">
-        <v>0.09069997428781192</v>
+        <v>0.09174807694638604</v>
       </c>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="n">
@@ -3925,7 +3925,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>5513.555555555556</v>
+        <v>5590.25</v>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
@@ -3934,7 +3934,7 @@
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="n">
-        <v>0.2425057998126882</v>
+        <v>0.245407983624745</v>
       </c>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="n">
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>3966.463414634146</v>
+        <v>3974.125</v>
       </c>
       <c r="C99" t="n">
         <v>0.9873305542186783</v>
@@ -4220,7 +4220,7 @@
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
-        <v>0.1512189297571995</v>
+        <v>0.1545198425930906</v>
       </c>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="n">
